--- a/Team-Data/2008-09/1-3-2008-09.xlsx
+++ b/Team-Data/2008-09/1-3-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,58 +728,58 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2" t="n">
         <v>11</v>
       </c>
       <c r="G2" t="n">
-        <v>0.667</v>
+        <v>0.656</v>
       </c>
       <c r="H2" t="n">
         <v>48.2</v>
       </c>
       <c r="I2" t="n">
-        <v>36</v>
+        <v>35.8</v>
       </c>
       <c r="J2" t="n">
-        <v>78.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.46</v>
+        <v>0.456</v>
       </c>
       <c r="L2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="N2" t="n">
         <v>0.381</v>
       </c>
       <c r="O2" t="n">
-        <v>17.9</v>
+        <v>18.1</v>
       </c>
       <c r="P2" t="n">
-        <v>23.9</v>
+        <v>24.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.748</v>
+        <v>0.745</v>
       </c>
       <c r="R2" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="S2" t="n">
-        <v>30.1</v>
+        <v>30.3</v>
       </c>
       <c r="T2" t="n">
-        <v>41</v>
+        <v>41.3</v>
       </c>
       <c r="U2" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="V2" t="n">
         <v>13.4</v>
@@ -724,22 +791,22 @@
         <v>5.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>98.2</v>
+        <v>98</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
         <v>6</v>
@@ -748,22 +815,22 @@
         <v>6</v>
       </c>
       <c r="AG2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH2" t="n">
         <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AJ2" t="n">
         <v>24</v>
       </c>
       <c r="AK2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM2" t="n">
         <v>3</v>
@@ -772,43 +839,43 @@
         <v>7</v>
       </c>
       <c r="AO2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT2" t="n">
         <v>17</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>18</v>
       </c>
       <c r="AU2" t="n">
         <v>8</v>
       </c>
       <c r="AV2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ2" t="n">
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
         <v>15</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -843,58 +910,58 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F3" t="n">
         <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.848</v>
+        <v>0.853</v>
       </c>
       <c r="H3" t="n">
         <v>48.3</v>
       </c>
       <c r="I3" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J3" t="n">
-        <v>75.8</v>
+        <v>75.7</v>
       </c>
       <c r="K3" t="n">
-        <v>0.487</v>
+        <v>0.485</v>
       </c>
       <c r="L3" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M3" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.378</v>
+        <v>0.373</v>
       </c>
       <c r="O3" t="n">
         <v>21.7</v>
       </c>
       <c r="P3" t="n">
-        <v>28.2</v>
+        <v>28.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.768</v>
+        <v>0.763</v>
       </c>
       <c r="R3" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S3" t="n">
-        <v>32.6</v>
+        <v>32.4</v>
       </c>
       <c r="T3" t="n">
-        <v>43.2</v>
+        <v>43</v>
       </c>
       <c r="U3" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="V3" t="n">
         <v>16.4</v>
@@ -903,43 +970,43 @@
         <v>8.699999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
         <v>4.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="AA3" t="n">
         <v>24.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.6</v>
+        <v>101.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK3" t="n">
         <v>2</v>
@@ -951,7 +1018,7 @@
         <v>22</v>
       </c>
       <c r="AN3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AO3" t="n">
         <v>3</v>
@@ -960,19 +1027,19 @@
         <v>3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV3" t="n">
         <v>30</v>
@@ -981,10 +1048,10 @@
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
         <v>26</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -1025,28 +1092,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
         <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>0.353</v>
+        <v>0.333</v>
       </c>
       <c r="H4" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I4" t="n">
         <v>33.6</v>
       </c>
       <c r="J4" t="n">
-        <v>75.7</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L4" t="n">
         <v>5.3</v>
@@ -1055,37 +1122,37 @@
         <v>15.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.351</v>
+        <v>0.35</v>
       </c>
       <c r="O4" t="n">
-        <v>18.7</v>
+        <v>18.4</v>
       </c>
       <c r="P4" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.744</v>
+        <v>0.738</v>
       </c>
       <c r="R4" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S4" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="T4" t="n">
-        <v>39.1</v>
+        <v>39.3</v>
       </c>
       <c r="U4" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="V4" t="n">
         <v>15.6</v>
       </c>
       <c r="W4" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y4" t="n">
         <v>6.1</v>
@@ -1097,16 +1164,16 @@
         <v>21.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>91.2</v>
+        <v>90.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.6</v>
+        <v>-3</v>
       </c>
       <c r="AD4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF4" t="n">
         <v>23</v>
@@ -1115,16 +1182,16 @@
         <v>23</v>
       </c>
       <c r="AH4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
       </c>
       <c r="AJ4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL4" t="n">
         <v>21</v>
@@ -1136,34 +1203,34 @@
         <v>18</v>
       </c>
       <c r="AO4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR4" t="n">
         <v>19</v>
       </c>
       <c r="AS4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AT4" t="n">
         <v>28</v>
       </c>
       <c r="AU4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW4" t="n">
         <v>21</v>
       </c>
       <c r="AX4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY4" t="n">
         <v>29</v>
@@ -1172,13 +1239,13 @@
         <v>19</v>
       </c>
       <c r="BA4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
       </c>
       <c r="BC4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -1210,13 +1277,13 @@
         <v>33</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5" t="n">
-        <v>0.394</v>
+        <v>0.424</v>
       </c>
       <c r="H5" t="n">
         <v>48.5</v>
@@ -1225,109 +1292,109 @@
         <v>37.2</v>
       </c>
       <c r="J5" t="n">
-        <v>84.40000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.44</v>
+        <v>0.444</v>
       </c>
       <c r="L5" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M5" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.384</v>
+        <v>0.386</v>
       </c>
       <c r="O5" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="P5" t="n">
-        <v>23.2</v>
+        <v>23.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.796</v>
+        <v>0.795</v>
       </c>
       <c r="R5" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S5" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T5" t="n">
         <v>41.9</v>
       </c>
       <c r="U5" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="V5" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="W5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="X5" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>20</v>
+        <v>20.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>99.3</v>
+        <v>99.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>-4.3</v>
+        <v>-3.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
       </c>
       <c r="AF5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG5" t="n">
         <v>18</v>
       </c>
       <c r="AH5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI5" t="n">
         <v>9</v>
       </c>
       <c r="AJ5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AN5" t="n">
         <v>4</v>
       </c>
-      <c r="AK5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>6</v>
-      </c>
       <c r="AO5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AP5" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AQ5" t="n">
         <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AS5" t="n">
         <v>13</v>
@@ -1336,31 +1403,31 @@
         <v>13</v>
       </c>
       <c r="AU5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV5" t="n">
         <v>18</v>
       </c>
       <c r="AW5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AX5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AY5" t="n">
         <v>27</v>
       </c>
       <c r="AZ5" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA5" t="n">
         <v>23</v>
       </c>
-      <c r="BA5" t="n">
-        <v>24</v>
-      </c>
       <c r="BB5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -1389,85 +1456,85 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6" t="n">
         <v>27</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.871</v>
+        <v>0.844</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>37.9</v>
+        <v>37.7</v>
       </c>
       <c r="J6" t="n">
-        <v>79.2</v>
+        <v>78.8</v>
       </c>
       <c r="K6" t="n">
-        <v>0.479</v>
+        <v>0.478</v>
       </c>
       <c r="L6" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M6" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.35</v>
+        <v>0.346</v>
       </c>
       <c r="O6" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="P6" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.771</v>
+        <v>0.769</v>
       </c>
       <c r="R6" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S6" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="T6" t="n">
         <v>42.2</v>
       </c>
       <c r="U6" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V6" t="n">
-        <v>12.8</v>
+        <v>13.1</v>
       </c>
       <c r="W6" t="n">
         <v>8.1</v>
       </c>
       <c r="X6" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>102.5</v>
+        <v>101.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>12.8</v>
+        <v>12.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1476,16 +1543,16 @@
         <v>1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
         <v>27</v>
       </c>
       <c r="AI6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AK6" t="n">
         <v>3</v>
@@ -1497,16 +1564,16 @@
         <v>7</v>
       </c>
       <c r="AN6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR6" t="n">
         <v>15</v>
@@ -1518,10 +1585,10 @@
         <v>12</v>
       </c>
       <c r="AU6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AW6" t="n">
         <v>7</v>
@@ -1533,10 +1600,10 @@
         <v>1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BB6" t="n">
         <v>7</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>3.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AE7" t="n">
         <v>9</v>
@@ -1664,7 +1731,7 @@
         <v>8</v>
       </c>
       <c r="AI7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ7" t="n">
         <v>7</v>
@@ -1676,10 +1743,10 @@
         <v>11</v>
       </c>
       <c r="AM7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO7" t="n">
         <v>26</v>
@@ -1700,19 +1767,19 @@
         <v>1</v>
       </c>
       <c r="AU7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AV7" t="n">
         <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX7" t="n">
         <v>12</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ7" t="n">
         <v>1</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F8" t="n">
         <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>0.657</v>
+        <v>0.647</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
@@ -1771,49 +1838,49 @@
         <v>36.8</v>
       </c>
       <c r="J8" t="n">
-        <v>78.09999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="K8" t="n">
-        <v>0.471</v>
+        <v>0.47</v>
       </c>
       <c r="L8" t="n">
         <v>6.9</v>
       </c>
       <c r="M8" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0.385</v>
+        <v>0.384</v>
       </c>
       <c r="O8" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="P8" t="n">
-        <v>30.1</v>
+        <v>29.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.76</v>
+        <v>0.762</v>
       </c>
       <c r="R8" t="n">
         <v>10.3</v>
       </c>
       <c r="S8" t="n">
-        <v>30.1</v>
+        <v>30.3</v>
       </c>
       <c r="T8" t="n">
-        <v>40.4</v>
+        <v>40.6</v>
       </c>
       <c r="U8" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="V8" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W8" t="n">
         <v>8.9</v>
       </c>
       <c r="X8" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y8" t="n">
         <v>5.8</v>
@@ -1822,16 +1889,16 @@
         <v>22.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="AB8" t="n">
         <v>103.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1846,7 +1913,7 @@
         <v>26</v>
       </c>
       <c r="AI8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AJ8" t="n">
         <v>25</v>
@@ -1855,13 +1922,13 @@
         <v>6</v>
       </c>
       <c r="AL8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM8" t="n">
         <v>15</v>
       </c>
       <c r="AN8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1870,34 +1937,34 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS8" t="n">
         <v>14</v>
       </c>
       <c r="AT8" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AU8" t="n">
         <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW8" t="n">
         <v>3</v>
       </c>
       <c r="AX8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY8" t="n">
         <v>25</v>
       </c>
       <c r="AZ8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA8" t="n">
         <v>4</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -2034,10 +2101,10 @@
         <v>23</v>
       </c>
       <c r="AK9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AL9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM9" t="n">
         <v>27</v>
@@ -2046,7 +2113,7 @@
         <v>15</v>
       </c>
       <c r="AO9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP9" t="n">
         <v>20</v>
@@ -2058,19 +2125,19 @@
         <v>23</v>
       </c>
       <c r="AS9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT9" t="n">
         <v>21</v>
       </c>
       <c r="AU9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX9" t="n">
         <v>9</v>
@@ -2085,7 +2152,7 @@
         <v>20</v>
       </c>
       <c r="BB9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC9" t="n">
         <v>14</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2283,7 @@
         <v>2</v>
       </c>
       <c r="AK10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL10" t="n">
         <v>18</v>
@@ -2240,16 +2307,16 @@
         <v>3</v>
       </c>
       <c r="AS10" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AT10" t="n">
         <v>10</v>
       </c>
       <c r="AU10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW10" t="n">
         <v>5</v>
@@ -2261,7 +2328,7 @@
         <v>28</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA10" t="n">
         <v>1</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -2299,58 +2366,58 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E11" t="n">
         <v>21</v>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6</v>
+        <v>0.618</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
       </c>
       <c r="I11" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="J11" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L11" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M11" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.377</v>
+        <v>0.375</v>
       </c>
       <c r="O11" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="P11" t="n">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S11" t="n">
-        <v>32.4</v>
+        <v>32.6</v>
       </c>
       <c r="T11" t="n">
-        <v>42.9</v>
+        <v>43.1</v>
       </c>
       <c r="U11" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V11" t="n">
         <v>14.1</v>
@@ -2359,37 +2426,37 @@
         <v>6.6</v>
       </c>
       <c r="X11" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y11" t="n">
         <v>5.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="AA11" t="n">
         <v>21.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>97</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AF11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI11" t="n">
         <v>29</v>
@@ -2398,7 +2465,7 @@
         <v>17</v>
       </c>
       <c r="AK11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL11" t="n">
         <v>8</v>
@@ -2413,7 +2480,7 @@
         <v>7</v>
       </c>
       <c r="AP11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ11" t="n">
         <v>2</v>
@@ -2422,13 +2489,13 @@
         <v>22</v>
       </c>
       <c r="AS11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AV11" t="n">
         <v>13</v>
@@ -2437,19 +2504,19 @@
         <v>26</v>
       </c>
       <c r="AX11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ11" t="n">
         <v>2</v>
       </c>
       <c r="BA11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BB11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC11" t="n">
         <v>11</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -2481,28 +2548,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F12" t="n">
         <v>21</v>
       </c>
       <c r="G12" t="n">
-        <v>0.364</v>
+        <v>0.344</v>
       </c>
       <c r="H12" t="n">
         <v>48.8</v>
       </c>
       <c r="I12" t="n">
-        <v>39</v>
+        <v>38.8</v>
       </c>
       <c r="J12" t="n">
         <v>86.09999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.453</v>
+        <v>0.451</v>
       </c>
       <c r="L12" t="n">
         <v>6.9</v>
@@ -2511,16 +2578,16 @@
         <v>19.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="O12" t="n">
-        <v>18.1</v>
+        <v>17.7</v>
       </c>
       <c r="P12" t="n">
-        <v>22.5</v>
+        <v>22.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.802</v>
+        <v>0.8</v>
       </c>
       <c r="R12" t="n">
         <v>12.1</v>
@@ -2532,37 +2599,37 @@
         <v>44.8</v>
       </c>
       <c r="U12" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="V12" t="n">
         <v>15.9</v>
       </c>
       <c r="W12" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="X12" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y12" t="n">
         <v>5.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>102.9</v>
+        <v>102.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2</v>
+        <v>-2.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF12" t="n">
         <v>22</v>
@@ -2583,7 +2650,7 @@
         <v>14</v>
       </c>
       <c r="AL12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM12" t="n">
         <v>11</v>
@@ -2592,25 +2659,25 @@
         <v>17</v>
       </c>
       <c r="AO12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AP12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AQ12" t="n">
         <v>5</v>
       </c>
       <c r="AR12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS12" t="n">
         <v>2</v>
       </c>
       <c r="AT12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV12" t="n">
         <v>26</v>
@@ -2619,7 +2686,7 @@
         <v>16</v>
       </c>
       <c r="AX12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AY12" t="n">
         <v>26</v>
@@ -2628,7 +2695,7 @@
         <v>27</v>
       </c>
       <c r="BA12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BB12" t="n">
         <v>6</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-6.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
         <v>26</v>
@@ -2759,7 +2826,7 @@
         <v>25</v>
       </c>
       <c r="AJ13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK13" t="n">
         <v>30</v>
@@ -2768,7 +2835,7 @@
         <v>23</v>
       </c>
       <c r="AM13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN13" t="n">
         <v>29</v>
@@ -2777,7 +2844,7 @@
         <v>27</v>
       </c>
       <c r="AP13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ13" t="n">
         <v>23</v>
@@ -2792,13 +2859,13 @@
         <v>11</v>
       </c>
       <c r="AU13" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AV13" t="n">
         <v>17</v>
       </c>
       <c r="AW13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
@@ -2816,7 +2883,7 @@
         <v>29</v>
       </c>
       <c r="BC13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F14" t="n">
         <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>0.833</v>
+        <v>0.839</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>39.8</v>
+        <v>39.7</v>
       </c>
       <c r="J14" t="n">
-        <v>84.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="K14" t="n">
         <v>0.473</v>
@@ -2872,31 +2939,31 @@
         <v>6.7</v>
       </c>
       <c r="M14" t="n">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="N14" t="n">
-        <v>0.367</v>
+        <v>0.373</v>
       </c>
       <c r="O14" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="P14" t="n">
-        <v>28.2</v>
+        <v>27.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.764</v>
+        <v>0.766</v>
       </c>
       <c r="R14" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="S14" t="n">
-        <v>32.2</v>
+        <v>32.5</v>
       </c>
       <c r="T14" t="n">
-        <v>44.7</v>
+        <v>44.9</v>
       </c>
       <c r="U14" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="V14" t="n">
         <v>14</v>
@@ -2908,28 +2975,28 @@
         <v>5.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.8</v>
+        <v>107.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AE14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="n">
         <v>3</v>
@@ -2941,10 +3008,10 @@
         <v>1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL14" t="n">
         <v>15</v>
@@ -2953,7 +3020,7 @@
         <v>14</v>
       </c>
       <c r="AN14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO14" t="n">
         <v>4</v>
@@ -2962,16 +3029,16 @@
         <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR14" t="n">
         <v>6</v>
       </c>
       <c r="AS14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="n">
         <v>2</v>
@@ -2983,13 +3050,13 @@
         <v>1</v>
       </c>
       <c r="AX14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-5.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE15" t="n">
         <v>24</v>
@@ -3141,10 +3208,10 @@
         <v>12</v>
       </c>
       <c r="AP15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR15" t="n">
         <v>26</v>
@@ -3162,7 +3229,7 @@
         <v>16</v>
       </c>
       <c r="AW15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX15" t="n">
         <v>22</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -3209,157 +3276,157 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F16" t="n">
         <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.548</v>
       </c>
       <c r="H16" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I16" t="n">
-        <v>35.9</v>
+        <v>36.1</v>
       </c>
       <c r="J16" t="n">
-        <v>80.7</v>
+        <v>80.8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L16" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M16" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0.349</v>
+        <v>0.347</v>
       </c>
       <c r="O16" t="n">
-        <v>17.3</v>
+        <v>16.9</v>
       </c>
       <c r="P16" t="n">
-        <v>23.6</v>
+        <v>23.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.735</v>
+        <v>0.733</v>
       </c>
       <c r="R16" t="n">
         <v>11</v>
       </c>
       <c r="S16" t="n">
-        <v>29.7</v>
+        <v>29.5</v>
       </c>
       <c r="T16" t="n">
-        <v>40.7</v>
+        <v>40.5</v>
       </c>
       <c r="U16" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="V16" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="W16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X16" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z16" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.2</v>
+        <v>19.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>96</v>
+        <v>95.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AE16" t="n">
         <v>15</v>
       </c>
       <c r="AF16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH16" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AI16" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AJ16" t="n">
         <v>15</v>
       </c>
       <c r="AK16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM16" t="n">
         <v>9</v>
       </c>
       <c r="AN16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO16" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AP16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ16" t="n">
         <v>29</v>
       </c>
       <c r="AR16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AT16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AU16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW16" t="n">
         <v>6</v>
       </c>
       <c r="AX16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AZ16" t="n">
         <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC16" t="n">
         <v>16</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -3409,106 +3476,106 @@
         <v>35.9</v>
       </c>
       <c r="J17" t="n">
-        <v>81.7</v>
+        <v>82</v>
       </c>
       <c r="K17" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="M17" t="n">
         <v>14.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0.333</v>
+        <v>0.337</v>
       </c>
       <c r="O17" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="P17" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.776</v>
+        <v>0.778</v>
       </c>
       <c r="R17" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="S17" t="n">
-        <v>30.9</v>
+        <v>30.7</v>
       </c>
       <c r="T17" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="U17" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V17" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W17" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X17" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.1</v>
+        <v>24.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="AB17" t="n">
         <v>96.59999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE17" t="n">
         <v>16</v>
       </c>
       <c r="AF17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AJ17" t="n">
         <v>10</v>
       </c>
       <c r="AK17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL17" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AM17" t="n">
         <v>25</v>
       </c>
       <c r="AN17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO17" t="n">
         <v>9</v>
       </c>
       <c r="AP17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR17" t="n">
         <v>4</v>
@@ -3520,19 +3587,19 @@
         <v>4</v>
       </c>
       <c r="AU17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AY17" t="n">
         <v>15</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>28</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>14</v>
       </c>
       <c r="AZ17" t="n">
         <v>30</v>
@@ -3541,7 +3608,7 @@
         <v>6</v>
       </c>
       <c r="BB17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC17" t="n">
         <v>15</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F18" t="n">
         <v>25</v>
       </c>
       <c r="G18" t="n">
-        <v>0.242</v>
+        <v>0.219</v>
       </c>
       <c r="H18" t="n">
         <v>48.6</v>
@@ -3591,82 +3658,82 @@
         <v>36.1</v>
       </c>
       <c r="J18" t="n">
-        <v>83.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="K18" t="n">
-        <v>0.433</v>
+        <v>0.434</v>
       </c>
       <c r="L18" t="n">
         <v>5</v>
       </c>
       <c r="M18" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="N18" t="n">
-        <v>0.329</v>
+        <v>0.331</v>
       </c>
       <c r="O18" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="P18" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.762</v>
+        <v>0.759</v>
       </c>
       <c r="R18" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="S18" t="n">
-        <v>29.7</v>
+        <v>29.5</v>
       </c>
       <c r="T18" t="n">
-        <v>41.8</v>
+        <v>41.6</v>
       </c>
       <c r="U18" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="V18" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W18" t="n">
         <v>6.3</v>
       </c>
       <c r="X18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>96.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>-6</v>
+        <v>-6.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE18" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AF18" t="n">
         <v>26</v>
       </c>
       <c r="AG18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ18" t="n">
         <v>8</v>
@@ -3675,7 +3742,7 @@
         <v>29</v>
       </c>
       <c r="AL18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM18" t="n">
         <v>24</v>
@@ -3684,28 +3751,28 @@
         <v>25</v>
       </c>
       <c r="AO18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU18" t="n">
         <v>17</v>
       </c>
       <c r="AV18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW18" t="n">
         <v>29</v>
@@ -3717,16 +3784,16 @@
         <v>30</v>
       </c>
       <c r="AZ18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA18" t="n">
         <v>16</v>
       </c>
       <c r="BB18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -3755,85 +3822,85 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E19" t="n">
         <v>16</v>
       </c>
       <c r="F19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G19" t="n">
-        <v>0.471</v>
+        <v>0.485</v>
       </c>
       <c r="H19" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="I19" t="n">
         <v>35.6</v>
       </c>
       <c r="J19" t="n">
-        <v>81.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="K19" t="n">
-        <v>0.437</v>
+        <v>0.438</v>
       </c>
       <c r="L19" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M19" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="N19" t="n">
-        <v>0.37</v>
+        <v>0.371</v>
       </c>
       <c r="O19" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="P19" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.789</v>
+        <v>0.788</v>
       </c>
       <c r="R19" t="n">
         <v>11.5</v>
       </c>
       <c r="S19" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T19" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="U19" t="n">
         <v>18.7</v>
       </c>
       <c r="V19" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="W19" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z19" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>99.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.6</v>
+        <v>-2.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
@@ -3845,25 +3912,25 @@
         <v>16</v>
       </c>
       <c r="AH19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI19" t="n">
         <v>26</v>
       </c>
       <c r="AJ19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
         <v>6</v>
       </c>
       <c r="AM19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO19" t="n">
         <v>5</v>
@@ -3875,37 +3942,37 @@
         <v>9</v>
       </c>
       <c r="AR19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU19" t="n">
         <v>29</v>
       </c>
       <c r="AV19" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AW19" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AX19" t="n">
         <v>19</v>
       </c>
       <c r="AY19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ19" t="n">
         <v>28</v>
       </c>
       <c r="BA19" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BB19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC19" t="n">
         <v>19</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -3937,43 +4004,43 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E20" t="n">
         <v>20</v>
       </c>
       <c r="F20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>0.667</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H20" t="n">
         <v>48</v>
       </c>
       <c r="I20" t="n">
-        <v>34.9</v>
+        <v>34.8</v>
       </c>
       <c r="J20" t="n">
-        <v>76.40000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="K20" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L20" t="n">
         <v>7.6</v>
       </c>
       <c r="M20" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.392</v>
+        <v>0.395</v>
       </c>
       <c r="O20" t="n">
         <v>17.9</v>
       </c>
       <c r="P20" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="Q20" t="n">
         <v>0.803</v>
@@ -3982,40 +4049,40 @@
         <v>9.800000000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="T20" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="U20" t="n">
         <v>20</v>
       </c>
       <c r="V20" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="W20" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X20" t="n">
         <v>4.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Z20" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>95.2</v>
+        <v>95</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE20" t="n">
         <v>9</v>
@@ -4036,7 +4103,7 @@
         <v>27</v>
       </c>
       <c r="AK20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL20" t="n">
         <v>7</v>
@@ -4051,7 +4118,7 @@
         <v>24</v>
       </c>
       <c r="AP20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ20" t="n">
         <v>4</v>
@@ -4066,10 +4133,10 @@
         <v>29</v>
       </c>
       <c r="AU20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW20" t="n">
         <v>8</v>
@@ -4081,16 +4148,16 @@
         <v>3</v>
       </c>
       <c r="AZ20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA20" t="n">
         <v>12</v>
       </c>
       <c r="BB20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -4209,16 +4276,16 @@
         <v>21</v>
       </c>
       <c r="AH21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ21" t="n">
         <v>1</v>
       </c>
       <c r="AK21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4233,16 +4300,16 @@
         <v>22</v>
       </c>
       <c r="AP21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ21" t="n">
         <v>6</v>
       </c>
       <c r="AR21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT21" t="n">
         <v>9</v>
@@ -4251,10 +4318,10 @@
         <v>6</v>
       </c>
       <c r="AV21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4272,7 +4339,7 @@
         <v>3</v>
       </c>
       <c r="BC21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-8.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="n">
         <v>30</v>
@@ -4409,28 +4476,28 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AO22" t="n">
         <v>20</v>
       </c>
       <c r="AP22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ22" t="n">
         <v>24</v>
       </c>
       <c r="AR22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS22" t="n">
         <v>18</v>
       </c>
       <c r="AT22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV22" t="n">
         <v>27</v>
@@ -4451,7 +4518,7 @@
         <v>25</v>
       </c>
       <c r="BB22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC22" t="n">
         <v>29</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>7.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE23" t="n">
         <v>3</v>
@@ -4573,16 +4640,16 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ23" t="n">
         <v>21</v>
       </c>
       <c r="AK23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AL23" t="n">
         <v>2</v>
@@ -4594,7 +4661,7 @@
         <v>9</v>
       </c>
       <c r="AO23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP23" t="n">
         <v>7</v>
@@ -4603,7 +4670,7 @@
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS23" t="n">
         <v>3</v>
@@ -4615,10 +4682,10 @@
         <v>28</v>
       </c>
       <c r="AV23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX23" t="n">
         <v>3</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -4665,28 +4732,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E24" t="n">
         <v>13</v>
       </c>
       <c r="F24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G24" t="n">
-        <v>0.394</v>
+        <v>0.406</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>36.4</v>
+        <v>36.2</v>
       </c>
       <c r="J24" t="n">
-        <v>81.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.448</v>
+        <v>0.445</v>
       </c>
       <c r="L24" t="n">
         <v>3.6</v>
@@ -4695,16 +4762,16 @@
         <v>12.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0.294</v>
+        <v>0.293</v>
       </c>
       <c r="O24" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="P24" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.743</v>
+        <v>0.741</v>
       </c>
       <c r="R24" t="n">
         <v>12.9</v>
@@ -4713,16 +4780,16 @@
         <v>30.5</v>
       </c>
       <c r="T24" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="U24" t="n">
         <v>20.1</v>
       </c>
       <c r="V24" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="W24" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X24" t="n">
         <v>5.1</v>
@@ -4731,28 +4798,28 @@
         <v>5.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>94.7</v>
+        <v>94.3</v>
       </c>
       <c r="AC24" t="n">
         <v>-1.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF24" t="n">
         <v>18</v>
       </c>
-      <c r="AF24" t="n">
+      <c r="AG24" t="n">
         <v>19</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>18</v>
       </c>
       <c r="AH24" t="n">
         <v>23</v>
@@ -4761,10 +4828,10 @@
         <v>13</v>
       </c>
       <c r="AJ24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL24" t="n">
         <v>30</v>
@@ -4776,13 +4843,13 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP24" t="n">
         <v>15</v>
       </c>
       <c r="AQ24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR24" t="n">
         <v>2</v>
@@ -4797,13 +4864,13 @@
         <v>18</v>
       </c>
       <c r="AV24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW24" t="n">
         <v>9</v>
       </c>
       <c r="AX24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY24" t="n">
         <v>21</v>
@@ -4815,7 +4882,7 @@
         <v>21</v>
       </c>
       <c r="BB24" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BC24" t="n">
         <v>17</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -4937,7 +5004,7 @@
         <v>12</v>
       </c>
       <c r="AH25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI25" t="n">
         <v>4</v>
@@ -4964,7 +5031,7 @@
         <v>5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR25" t="n">
         <v>28</v>
@@ -4973,7 +5040,7 @@
         <v>9</v>
       </c>
       <c r="AT25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU25" t="n">
         <v>11</v>
@@ -4988,10 +5055,10 @@
         <v>18</v>
       </c>
       <c r="AY25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA25" t="n">
         <v>8</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -5029,61 +5096,61 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E26" t="n">
         <v>20</v>
       </c>
       <c r="F26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G26" t="n">
-        <v>0.625</v>
+        <v>0.606</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
       </c>
       <c r="I26" t="n">
-        <v>36.4</v>
+        <v>36.2</v>
       </c>
       <c r="J26" t="n">
-        <v>79</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.461</v>
+        <v>0.457</v>
       </c>
       <c r="L26" t="n">
         <v>7.8</v>
       </c>
       <c r="M26" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0.384</v>
+        <v>0.386</v>
       </c>
       <c r="O26" t="n">
-        <v>18.4</v>
+        <v>18.1</v>
       </c>
       <c r="P26" t="n">
-        <v>23.6</v>
+        <v>23.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.78</v>
+        <v>0.777</v>
       </c>
       <c r="R26" t="n">
         <v>13.1</v>
       </c>
       <c r="S26" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="T26" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="U26" t="n">
         <v>20.5</v>
       </c>
       <c r="V26" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W26" t="n">
         <v>6.9</v>
@@ -5092,43 +5159,43 @@
         <v>5.3</v>
       </c>
       <c r="Y26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="AC26" t="n">
         <v>3.4</v>
       </c>
-      <c r="Z26" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>99</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AD26" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AE26" t="n">
         <v>9</v>
       </c>
       <c r="AF26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH26" t="n">
         <v>9</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>8</v>
       </c>
       <c r="AI26" t="n">
         <v>14</v>
       </c>
       <c r="AJ26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL26" t="n">
         <v>5</v>
@@ -5140,13 +5207,13 @@
         <v>5</v>
       </c>
       <c r="AO26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP26" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AQ26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5164,7 +5231,7 @@
         <v>3</v>
       </c>
       <c r="AW26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX26" t="n">
         <v>11</v>
@@ -5173,16 +5240,16 @@
         <v>2</v>
       </c>
       <c r="AZ26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BB26" t="n">
         <v>14</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -5211,127 +5278,127 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E27" t="n">
         <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G27" t="n">
-        <v>0.235</v>
+        <v>0.242</v>
       </c>
       <c r="H27" t="n">
         <v>48.3</v>
       </c>
       <c r="I27" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J27" t="n">
-        <v>81</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L27" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="M27" t="n">
-        <v>17.1</v>
+        <v>16.8</v>
       </c>
       <c r="N27" t="n">
-        <v>0.325</v>
+        <v>0.315</v>
       </c>
       <c r="O27" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="P27" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="Q27" t="n">
         <v>0.792</v>
       </c>
       <c r="R27" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S27" t="n">
         <v>28.9</v>
       </c>
       <c r="T27" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
       <c r="U27" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="V27" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="W27" t="n">
         <v>6.8</v>
       </c>
       <c r="X27" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y27" t="n">
         <v>5.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>96.40000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>-9.199999999999999</v>
+        <v>-9.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
       </c>
       <c r="AF27" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AG27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH27" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AI27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ27" t="n">
         <v>14</v>
       </c>
       <c r="AK27" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AL27" t="n">
         <v>20</v>
       </c>
       <c r="AM27" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AN27" t="n">
         <v>27</v>
       </c>
       <c r="AO27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ27" t="n">
         <v>8</v>
       </c>
       <c r="AR27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS27" t="n">
         <v>26</v>
@@ -5340,19 +5407,19 @@
         <v>26</v>
       </c>
       <c r="AU27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV27" t="n">
         <v>25</v>
       </c>
       <c r="AW27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX27" t="n">
         <v>24</v>
       </c>
       <c r="AY27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ27" t="n">
         <v>29</v>
@@ -5361,7 +5428,7 @@
         <v>10</v>
       </c>
       <c r="BB27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -5393,64 +5460,64 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F28" t="n">
         <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>0.667</v>
+        <v>0.656</v>
       </c>
       <c r="H28" t="n">
         <v>48.9</v>
       </c>
       <c r="I28" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J28" t="n">
         <v>79.2</v>
       </c>
       <c r="K28" t="n">
-        <v>0.466</v>
+        <v>0.463</v>
       </c>
       <c r="L28" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0.406</v>
+        <v>0.399</v>
       </c>
       <c r="O28" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="P28" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.751</v>
+        <v>0.753</v>
       </c>
       <c r="R28" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>31.6</v>
+        <v>31.9</v>
       </c>
       <c r="T28" t="n">
-        <v>40</v>
+        <v>40.3</v>
       </c>
       <c r="U28" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="V28" t="n">
         <v>12.2</v>
       </c>
       <c r="W28" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="X28" t="n">
         <v>4.2</v>
@@ -5462,16 +5529,16 @@
         <v>18.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.09999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="AC28" t="n">
         <v>3.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE28" t="n">
         <v>6</v>
@@ -5480,25 +5547,25 @@
         <v>6</v>
       </c>
       <c r="AG28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK28" t="n">
         <v>7</v>
       </c>
       <c r="AL28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN28" t="n">
         <v>1</v>
@@ -5510,19 +5577,19 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
       </c>
       <c r="AS28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV28" t="n">
         <v>1</v>
@@ -5534,7 +5601,7 @@
         <v>26</v>
       </c>
       <c r="AY28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ28" t="n">
         <v>3</v>
@@ -5543,7 +5610,7 @@
         <v>30</v>
       </c>
       <c r="BB28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC28" t="n">
         <v>7</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -5653,19 +5720,19 @@
         <v>-3</v>
       </c>
       <c r="AD29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF29" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AG29" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AH29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI29" t="n">
         <v>24</v>
@@ -5680,13 +5747,13 @@
         <v>16</v>
       </c>
       <c r="AM29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AN29" t="n">
         <v>8</v>
       </c>
       <c r="AO29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP29" t="n">
         <v>24</v>
@@ -5713,16 +5780,16 @@
         <v>28</v>
       </c>
       <c r="AX29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ29" t="n">
         <v>4</v>
       </c>
       <c r="BA29" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BB29" t="n">
         <v>18</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>2.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="n">
         <v>13</v>
@@ -5844,19 +5911,19 @@
         <v>15</v>
       </c>
       <c r="AG30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH30" t="n">
         <v>7</v>
       </c>
       <c r="AI30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ30" t="n">
         <v>16</v>
       </c>
       <c r="AK30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL30" t="n">
         <v>28</v>
@@ -5865,7 +5932,7 @@
         <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO30" t="n">
         <v>6</v>
@@ -5874,13 +5941,13 @@
         <v>6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR30" t="n">
         <v>7</v>
       </c>
       <c r="AS30" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AT30" t="n">
         <v>14</v>
@@ -5895,13 +5962,13 @@
         <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA30" t="n">
         <v>3</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6096,7 @@
         <v>29</v>
       </c>
       <c r="AH31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI31" t="n">
         <v>16</v>
@@ -6044,13 +6111,13 @@
         <v>22</v>
       </c>
       <c r="AM31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN31" t="n">
         <v>28</v>
       </c>
       <c r="AO31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP31" t="n">
         <v>25</v>
@@ -6062,19 +6129,19 @@
         <v>11</v>
       </c>
       <c r="AS31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW31" t="n">
         <v>13</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>12</v>
       </c>
       <c r="AX31" t="n">
         <v>25</v>
@@ -6083,13 +6150,13 @@
         <v>18</v>
       </c>
       <c r="AZ31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA31" t="n">
         <v>28</v>
       </c>
       <c r="BB31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC31" t="n">
         <v>28</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-3-2008-09</t>
+          <t>2009-01-03</t>
         </is>
       </c>
     </row>
